--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -1621,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119506872</v>
+        <v>119506797</v>
       </c>
       <c r="B10" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,34 +1637,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541229</v>
+        <v>541240</v>
       </c>
       <c r="R10" t="n">
-        <v>7246809</v>
+        <v>7246801</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,7 +1706,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fjolårets fruktkroppar</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,14 +1728,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Granstubbe, knäckt</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe, knäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119506797</v>
+        <v>119506872</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,39 +1764,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541240</v>
+        <v>541229</v>
       </c>
       <c r="R11" t="n">
-        <v>7246801</v>
+        <v>7246809</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,7 +1828,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,9 +1850,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Granstubbe, knäckt</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119506874</v>
+        <v>119506927</v>
       </c>
       <c r="B4" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541139</v>
+        <v>541118</v>
       </c>
       <c r="R4" t="n">
-        <v>7246736</v>
+        <v>7246705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,11 +997,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1010,26 +1005,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Stående</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1046,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119506927</v>
+        <v>119506874</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541118</v>
+        <v>541139</v>
       </c>
       <c r="R5" t="n">
-        <v>7246705</v>
+        <v>7246736</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,6 +1099,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1132,6 +1112,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Stående</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1621,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119506797</v>
+        <v>119506872</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,39 +1637,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541240</v>
+        <v>541229</v>
       </c>
       <c r="R10" t="n">
-        <v>7246801</v>
+        <v>7246809</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1701,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,9 +1723,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Granstubbe, knäckt</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119506872</v>
+        <v>119506797</v>
       </c>
       <c r="B11" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,34 +1764,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541229</v>
+        <v>541240</v>
       </c>
       <c r="R11" t="n">
-        <v>7246809</v>
+        <v>7246801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,7 +1833,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Fjolårets fruktkroppar</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,14 +1855,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granstubbe, knäckt</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe, knäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119506926</v>
+        <v>119506903</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541141</v>
+        <v>541113</v>
       </c>
       <c r="R21" t="n">
-        <v>7246733</v>
+        <v>7246660</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3022,6 +3022,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3038,10 +3058,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119506903</v>
+        <v>119506926</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3054,21 +3074,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3078,10 +3098,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541113</v>
+        <v>541141</v>
       </c>
       <c r="R22" t="n">
-        <v>7246660</v>
+        <v>7246733</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3124,26 +3144,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119506812</v>
+        <v>119506795</v>
       </c>
       <c r="B2" t="n">
-        <v>90509</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541217</v>
+        <v>541096</v>
       </c>
       <c r="R2" t="n">
-        <v>7246857</v>
+        <v>7246650</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +758,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -772,14 +782,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Granlåga mossbevuxen</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga mossbevuxen</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119506896</v>
+        <v>119506872</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,21 +818,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541157</v>
+        <v>541229</v>
       </c>
       <c r="R3" t="n">
-        <v>7246817</v>
+        <v>7246809</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,6 +880,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -896,12 +906,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119506874</v>
+        <v>119506786</v>
       </c>
       <c r="B5" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1047,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541139</v>
+        <v>541286</v>
       </c>
       <c r="R5" t="n">
-        <v>7246736</v>
+        <v>7246794</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1116,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fjolårets fruktkroppar</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,14 +1138,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Stående</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119506786</v>
+        <v>119506859</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>57421</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,20 +1170,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1181,10 +1191,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1193,10 +1207,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541286</v>
+        <v>541155</v>
       </c>
       <c r="R6" t="n">
-        <v>7246794</v>
+        <v>7246751</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,11 +1245,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1244,21 +1253,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1275,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119506923</v>
+        <v>119506812</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>90509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,21 +1285,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1315,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541274</v>
+        <v>541217</v>
       </c>
       <c r="R7" t="n">
-        <v>7246769</v>
+        <v>7246857</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,6 +1355,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Granlåga mossbevuxen</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga mossbevuxen</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1377,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119506818</v>
+        <v>119506924</v>
       </c>
       <c r="B8" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,21 +1407,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541160</v>
+        <v>541151</v>
       </c>
       <c r="R8" t="n">
-        <v>7246741</v>
+        <v>7246830</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1463,21 +1477,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1494,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119506796</v>
+        <v>119506896</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,39 +1509,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541119</v>
+        <v>541157</v>
       </c>
       <c r="R9" t="n">
-        <v>7246774</v>
+        <v>7246817</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,11 +1571,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Barksprätt, färska</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1601,9 +1590,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1621,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119506872</v>
+        <v>119506797</v>
       </c>
       <c r="B10" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,34 +1631,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541229</v>
+        <v>541240</v>
       </c>
       <c r="R10" t="n">
-        <v>7246809</v>
+        <v>7246801</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,7 +1700,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fjolårets fruktkroppar</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,14 +1722,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Granstubbe, knäckt</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe, knäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119506797</v>
+        <v>119506908</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,39 +1758,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541240</v>
+        <v>541157</v>
       </c>
       <c r="R11" t="n">
-        <v>7246801</v>
+        <v>7246738</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,11 +1820,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1855,9 +1839,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1875,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119506928</v>
+        <v>119506936</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>86196</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,34 +1880,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>249278</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541164</v>
+        <v>541297</v>
       </c>
       <c r="R12" t="n">
-        <v>7246746</v>
+        <v>7246784</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2099,10 +2092,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119506891</v>
+        <v>119506817</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>79608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,21 +2108,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2139,10 +2132,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541126</v>
+        <v>541174</v>
       </c>
       <c r="R14" t="n">
-        <v>7246674</v>
+        <v>7246843</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2177,6 +2170,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gammal sälg</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2188,22 +2186,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Granlåga och högstubbe</t>
+          <t>Gammal sälg</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga och högstubbe</t>
+          <t>Salix caprea # Gammal sälg</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2221,10 +2219,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119506906</v>
+        <v>119506928</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2237,21 +2235,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2261,10 +2259,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541184</v>
+        <v>541164</v>
       </c>
       <c r="R15" t="n">
-        <v>7246856</v>
+        <v>7246746</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2307,26 +2305,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2343,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119506936</v>
+        <v>119506805</v>
       </c>
       <c r="B16" t="n">
-        <v>86196</v>
+        <v>57463</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2359,21 +2337,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>249278</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2381,16 +2359,21 @@
           <t>2</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541297</v>
+        <v>541129</v>
       </c>
       <c r="R16" t="n">
-        <v>7246784</v>
+        <v>7246706</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2449,7 +2432,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119506795</v>
+        <v>119506787</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2485,7 +2468,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2494,10 +2477,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541096</v>
+        <v>541236</v>
       </c>
       <c r="R17" t="n">
-        <v>7246650</v>
+        <v>7246789</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,7 +2517,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Barksprätt, färska</t>
+          <t>Barksprätt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2576,10 +2559,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119506805</v>
+        <v>119506890</v>
       </c>
       <c r="B18" t="n">
-        <v>57463</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2592,43 +2575,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541129</v>
+        <v>541330</v>
       </c>
       <c r="R18" t="n">
-        <v>7246706</v>
+        <v>7246824</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2663,6 +2637,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2671,6 +2650,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2809,10 +2808,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119506787</v>
+        <v>119506818</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2825,39 +2824,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541236</v>
+        <v>541160</v>
       </c>
       <c r="R20" t="n">
-        <v>7246789</v>
+        <v>7246741</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2892,11 +2886,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2908,17 +2897,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2936,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119506903</v>
+        <v>119506827</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>91005</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2948,25 +2937,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2976,10 +2965,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541113</v>
+        <v>541223</v>
       </c>
       <c r="R21" t="n">
-        <v>7246660</v>
+        <v>7246768</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3058,7 +3047,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119506926</v>
+        <v>119506923</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -3098,10 +3087,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541141</v>
+        <v>541274</v>
       </c>
       <c r="R22" t="n">
-        <v>7246733</v>
+        <v>7246769</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3160,10 +3149,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119506827</v>
+        <v>119506903</v>
       </c>
       <c r="B23" t="n">
-        <v>91005</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3172,25 +3161,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3200,10 +3189,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541223</v>
+        <v>541113</v>
       </c>
       <c r="R23" t="n">
-        <v>7246768</v>
+        <v>7246660</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3282,10 +3271,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119506924</v>
+        <v>119506796</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3298,34 +3287,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541151</v>
+        <v>541119</v>
       </c>
       <c r="R24" t="n">
-        <v>7246830</v>
+        <v>7246774</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3360,6 +3354,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3368,6 +3367,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3384,7 +3398,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119506890</v>
+        <v>119506891</v>
       </c>
       <c r="B25" t="n">
         <v>90580</v>
@@ -3424,10 +3438,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541330</v>
+        <v>541126</v>
       </c>
       <c r="R25" t="n">
-        <v>7246824</v>
+        <v>7246674</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3462,11 +3476,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3488,12 +3497,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga och högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga och högstubbe</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3511,10 +3520,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119506817</v>
+        <v>119506906</v>
       </c>
       <c r="B26" t="n">
-        <v>79608</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3527,21 +3536,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3551,10 +3560,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541174</v>
+        <v>541184</v>
       </c>
       <c r="R26" t="n">
-        <v>7246843</v>
+        <v>7246856</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3589,11 +3598,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gammal sälg</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3605,22 +3609,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Gammal sälg</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Salix caprea # Gammal sälg</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3638,10 +3642,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119506908</v>
+        <v>119506874</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3654,21 +3658,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3678,10 +3682,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541157</v>
+        <v>541139</v>
       </c>
       <c r="R27" t="n">
-        <v>7246738</v>
+        <v>7246736</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3716,6 +3720,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3737,12 +3746,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Stående</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies # Stående</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3760,10 +3769,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119506859</v>
+        <v>119506926</v>
       </c>
       <c r="B28" t="n">
-        <v>57421</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3772,47 +3781,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541155</v>
+        <v>541141</v>
       </c>
       <c r="R28" t="n">
-        <v>7246751</v>
+        <v>7246733</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -1867,7 +1867,7 @@
         <v>119506936</v>
       </c>
       <c r="B12" t="n">
-        <v>86022</v>
+        <v>86025</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -1867,7 +1867,7 @@
         <v>119506936</v>
       </c>
       <c r="B12" t="n">
-        <v>86025</v>
+        <v>86031</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -1867,7 +1867,7 @@
         <v>119506936</v>
       </c>
       <c r="B12" t="n">
-        <v>86031</v>
+        <v>86034</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -1867,7 +1867,7 @@
         <v>119506936</v>
       </c>
       <c r="B12" t="n">
-        <v>86034</v>
+        <v>86038</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -1867,7 +1867,7 @@
         <v>119506936</v>
       </c>
       <c r="B12" t="n">
-        <v>86038</v>
+        <v>86039</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3873,6 +3873,703 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122118229</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78632</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Matsdal, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>541121</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7246580</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122118172</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Matsdal, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>541106</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7246534</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122118213</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90763</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Matsdal, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>541085</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7246493</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Granhögstubbe, knäckt</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122118203</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90763</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Matsdal, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>541108</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7246632</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>granhögstubbe knäckt med fågelbo i toppen</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122118171</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Matsdal, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>541115</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7246606</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122118230</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78632</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Matsdal, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>541091</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7246477</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Död gran</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gran</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -3875,10 +3875,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122118229</v>
+        <v>122118171</v>
       </c>
       <c r="B29" t="n">
-        <v>78632</v>
+        <v>57365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3891,34 +3891,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541121</v>
+        <v>541115</v>
       </c>
       <c r="R29" t="n">
-        <v>7246580</v>
+        <v>7246606</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3951,6 +3956,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3977,10 +3987,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122118172</v>
+        <v>122118229</v>
       </c>
       <c r="B30" t="n">
-        <v>57365</v>
+        <v>78632</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3993,39 +4003,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541106</v>
+        <v>541121</v>
       </c>
       <c r="R30" t="n">
-        <v>7246534</v>
+        <v>7246580</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4058,11 +4063,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska, lågt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4089,7 +4089,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122118213</v>
+        <v>122118203</v>
       </c>
       <c r="B31" t="n">
         <v>90763</v>
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541085</v>
+        <v>541108</v>
       </c>
       <c r="R31" t="n">
-        <v>7246493</v>
+        <v>7246632</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>granhögstubbe knäckt med fågelbo i toppen</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4211,7 +4211,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122118203</v>
+        <v>122118213</v>
       </c>
       <c r="B32" t="n">
         <v>90763</v>
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541108</v>
+        <v>541085</v>
       </c>
       <c r="R32" t="n">
-        <v>7246632</v>
+        <v>7246493</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4310,12 +4310,12 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>granhögstubbe knäckt med fågelbo i toppen</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4333,10 +4333,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122118171</v>
+        <v>122118230</v>
       </c>
       <c r="B33" t="n">
-        <v>57365</v>
+        <v>78632</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4349,39 +4349,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541115</v>
+        <v>541091</v>
       </c>
       <c r="R33" t="n">
-        <v>7246606</v>
+        <v>7246477</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4418,7 +4413,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska, lågt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4429,6 +4424,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Död gran</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gran</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4445,10 +4460,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122118230</v>
+        <v>122118172</v>
       </c>
       <c r="B34" t="n">
-        <v>78632</v>
+        <v>57365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4461,34 +4476,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541091</v>
+        <v>541106</v>
       </c>
       <c r="R34" t="n">
-        <v>7246477</v>
+        <v>7246534</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4525,7 +4545,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska, lågt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4536,26 +4556,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Död gran</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies # Död gran</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -3875,10 +3875,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122118171</v>
+        <v>122118213</v>
       </c>
       <c r="B29" t="n">
-        <v>57365</v>
+        <v>90772</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3891,39 +3891,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541115</v>
+        <v>541085</v>
       </c>
       <c r="R29" t="n">
-        <v>7246606</v>
+        <v>7246493</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3958,11 +3953,6 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack färska, lågt</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3971,6 +3961,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Granhögstubbe, knäckt</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3987,10 +3997,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122118229</v>
+        <v>122118230</v>
       </c>
       <c r="B30" t="n">
-        <v>78632</v>
+        <v>78639</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4027,10 +4037,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541121</v>
+        <v>541091</v>
       </c>
       <c r="R30" t="n">
-        <v>7246580</v>
+        <v>7246477</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,6 +4075,11 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4073,6 +4088,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Död gran</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gran</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4089,10 +4124,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122118203</v>
+        <v>122118172</v>
       </c>
       <c r="B31" t="n">
-        <v>90763</v>
+        <v>57369</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4105,34 +4140,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541108</v>
+        <v>541106</v>
       </c>
       <c r="R31" t="n">
-        <v>7246632</v>
+        <v>7246534</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4167,6 +4207,11 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4175,26 +4220,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>granhögstubbe knäckt med fågelbo i toppen</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4211,10 +4236,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122118213</v>
+        <v>122118171</v>
       </c>
       <c r="B32" t="n">
-        <v>90763</v>
+        <v>57369</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4227,34 +4252,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541085</v>
+        <v>541115</v>
       </c>
       <c r="R32" t="n">
-        <v>7246493</v>
+        <v>7246606</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4289,6 +4319,11 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4297,26 +4332,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4333,10 +4348,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122118230</v>
+        <v>122118203</v>
       </c>
       <c r="B33" t="n">
-        <v>78632</v>
+        <v>90772</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4349,21 +4364,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4373,10 +4388,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541091</v>
+        <v>541108</v>
       </c>
       <c r="R33" t="n">
-        <v>7246477</v>
+        <v>7246632</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4411,11 +4426,6 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4437,12 +4447,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>granhögstubbe knäckt med fågelbo i toppen</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4460,10 +4470,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122118172</v>
+        <v>122118229</v>
       </c>
       <c r="B34" t="n">
-        <v>57365</v>
+        <v>78639</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4476,39 +4486,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541106</v>
+        <v>541121</v>
       </c>
       <c r="R34" t="n">
-        <v>7246534</v>
+        <v>7246580</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4541,11 +4546,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska, lågt</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -3875,7 +3875,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122118172</v>
+        <v>122118171</v>
       </c>
       <c r="B29" t="n">
         <v>57374</v>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541106</v>
+        <v>541115</v>
       </c>
       <c r="R29" t="n">
-        <v>7246534</v>
+        <v>7246606</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3987,10 +3987,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122118230</v>
+        <v>122118203</v>
       </c>
       <c r="B30" t="n">
-        <v>78645</v>
+        <v>90797</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4003,21 +4003,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541091</v>
+        <v>541108</v>
       </c>
       <c r="R30" t="n">
-        <v>7246477</v>
+        <v>7246632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,11 +4065,6 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4091,12 +4086,12 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>granhögstubbe knäckt med fågelbo i toppen</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4114,7 +4109,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122118229</v>
+        <v>122118230</v>
       </c>
       <c r="B31" t="n">
         <v>78645</v>
@@ -4154,10 +4149,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541121</v>
+        <v>541091</v>
       </c>
       <c r="R31" t="n">
-        <v>7246580</v>
+        <v>7246477</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4192,6 +4187,11 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4200,6 +4200,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Död gran</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gran</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4216,7 +4236,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122118203</v>
+        <v>122118213</v>
       </c>
       <c r="B32" t="n">
         <v>90797</v>
@@ -4256,10 +4276,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541108</v>
+        <v>541085</v>
       </c>
       <c r="R32" t="n">
-        <v>7246632</v>
+        <v>7246493</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4315,12 +4335,12 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>granhögstubbe knäckt med fågelbo i toppen</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4338,10 +4358,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122118213</v>
+        <v>122118172</v>
       </c>
       <c r="B33" t="n">
-        <v>90797</v>
+        <v>57374</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4354,34 +4374,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541085</v>
+        <v>541106</v>
       </c>
       <c r="R33" t="n">
-        <v>7246493</v>
+        <v>7246534</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4416,6 +4441,11 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4424,26 +4454,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4460,10 +4470,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122118171</v>
+        <v>122118229</v>
       </c>
       <c r="B34" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4476,39 +4486,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541115</v>
+        <v>541121</v>
       </c>
       <c r="R34" t="n">
-        <v>7246606</v>
+        <v>7246580</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4541,11 +4546,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska, lågt</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -3875,10 +3875,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122118171</v>
+        <v>122118229</v>
       </c>
       <c r="B29" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3891,39 +3891,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541115</v>
+        <v>541121</v>
       </c>
       <c r="R29" t="n">
-        <v>7246606</v>
+        <v>7246580</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3956,11 +3951,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack färska, lågt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3987,10 +3977,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122118203</v>
+        <v>122118171</v>
       </c>
       <c r="B30" t="n">
-        <v>90797</v>
+        <v>57374</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4003,34 +3993,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541108</v>
+        <v>541115</v>
       </c>
       <c r="R30" t="n">
-        <v>7246632</v>
+        <v>7246606</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,6 +4060,11 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4073,26 +4073,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>granhögstubbe knäckt med fågelbo i toppen</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4109,10 +4089,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122118230</v>
+        <v>122118203</v>
       </c>
       <c r="B31" t="n">
-        <v>78645</v>
+        <v>90807</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4125,21 +4105,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4149,10 +4129,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541091</v>
+        <v>541108</v>
       </c>
       <c r="R31" t="n">
-        <v>7246477</v>
+        <v>7246632</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4187,11 +4167,6 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4213,12 +4188,12 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>granhögstubbe knäckt med fågelbo i toppen</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4236,10 +4211,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122118213</v>
+        <v>122118172</v>
       </c>
       <c r="B32" t="n">
-        <v>90797</v>
+        <v>57374</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4252,34 +4227,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541085</v>
+        <v>541106</v>
       </c>
       <c r="R32" t="n">
-        <v>7246493</v>
+        <v>7246534</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4314,6 +4294,11 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4322,26 +4307,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4358,10 +4323,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122118172</v>
+        <v>122118230</v>
       </c>
       <c r="B33" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4374,39 +4339,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541106</v>
+        <v>541091</v>
       </c>
       <c r="R33" t="n">
-        <v>7246534</v>
+        <v>7246477</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4443,7 +4403,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska, lågt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4454,6 +4414,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Död gran</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gran</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4470,10 +4450,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122118229</v>
+        <v>122118213</v>
       </c>
       <c r="B34" t="n">
-        <v>78645</v>
+        <v>90807</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4486,21 +4466,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4510,10 +4490,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541121</v>
+        <v>541085</v>
       </c>
       <c r="R34" t="n">
-        <v>7246580</v>
+        <v>7246493</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4556,6 +4536,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Granhögstubbe, knäckt</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -3875,10 +3875,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122118229</v>
+        <v>122118203</v>
       </c>
       <c r="B29" t="n">
-        <v>78646</v>
+        <v>90807</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3891,21 +3891,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541121</v>
+        <v>541108</v>
       </c>
       <c r="R29" t="n">
-        <v>7246580</v>
+        <v>7246632</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3961,6 +3961,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>granhögstubbe knäckt med fågelbo i toppen</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3977,10 +3997,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122118171</v>
+        <v>122118229</v>
       </c>
       <c r="B30" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3993,39 +4013,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541115</v>
+        <v>541121</v>
       </c>
       <c r="R30" t="n">
-        <v>7246606</v>
+        <v>7246580</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4058,11 +4073,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska, lågt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4089,7 +4099,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122118203</v>
+        <v>122118213</v>
       </c>
       <c r="B31" t="n">
         <v>90807</v>
@@ -4129,10 +4139,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541108</v>
+        <v>541085</v>
       </c>
       <c r="R31" t="n">
-        <v>7246632</v>
+        <v>7246493</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4188,12 +4198,12 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>granhögstubbe knäckt med fågelbo i toppen</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4211,10 +4221,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122118172</v>
+        <v>122118230</v>
       </c>
       <c r="B32" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4227,39 +4237,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541106</v>
+        <v>541091</v>
       </c>
       <c r="R32" t="n">
-        <v>7246534</v>
+        <v>7246477</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4296,7 +4301,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska, lågt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4307,6 +4312,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Död gran</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gran</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4323,10 +4348,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122118230</v>
+        <v>122118172</v>
       </c>
       <c r="B33" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4339,34 +4364,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541091</v>
+        <v>541106</v>
       </c>
       <c r="R33" t="n">
-        <v>7246477</v>
+        <v>7246534</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4403,7 +4433,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska, lågt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4414,26 +4444,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Död gran</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies # Död gran</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4450,10 +4460,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122118213</v>
+        <v>122118171</v>
       </c>
       <c r="B34" t="n">
-        <v>90807</v>
+        <v>57374</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4466,34 +4476,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541085</v>
+        <v>541115</v>
       </c>
       <c r="R34" t="n">
-        <v>7246493</v>
+        <v>7246606</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4528,6 +4543,11 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4536,26 +4556,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -3875,10 +3875,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122118203</v>
+        <v>122118172</v>
       </c>
       <c r="B29" t="n">
-        <v>90807</v>
+        <v>57379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3891,34 +3891,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541108</v>
+        <v>541106</v>
       </c>
       <c r="R29" t="n">
-        <v>7246632</v>
+        <v>7246534</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3953,6 +3958,11 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3961,26 +3971,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>granhögstubbe knäckt med fågelbo i toppen</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3997,10 +3987,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122118229</v>
+        <v>122118203</v>
       </c>
       <c r="B30" t="n">
-        <v>78646</v>
+        <v>90819</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4013,21 +4003,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4037,10 +4027,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541121</v>
+        <v>541108</v>
       </c>
       <c r="R30" t="n">
-        <v>7246580</v>
+        <v>7246632</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4083,6 +4073,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>granhögstubbe knäckt med fågelbo i toppen</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4102,7 +4112,7 @@
         <v>122118213</v>
       </c>
       <c r="B31" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4221,10 +4231,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122118230</v>
+        <v>122118229</v>
       </c>
       <c r="B32" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4261,10 +4271,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541091</v>
+        <v>541121</v>
       </c>
       <c r="R32" t="n">
-        <v>7246477</v>
+        <v>7246580</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4299,11 +4309,6 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4312,26 +4317,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Död gran</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies # Död gran</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4348,10 +4333,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122118172</v>
+        <v>122118171</v>
       </c>
       <c r="B33" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,10 +4378,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541106</v>
+        <v>541115</v>
       </c>
       <c r="R33" t="n">
-        <v>7246534</v>
+        <v>7246606</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4460,10 +4445,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122118171</v>
+        <v>122118230</v>
       </c>
       <c r="B34" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4476,39 +4461,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541115</v>
+        <v>541091</v>
       </c>
       <c r="R34" t="n">
-        <v>7246606</v>
+        <v>7246477</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4545,7 +4525,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska, lågt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4556,6 +4536,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Död gran</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gran</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -3875,7 +3875,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122118172</v>
+        <v>122118171</v>
       </c>
       <c r="B29" t="n">
         <v>57379</v>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541106</v>
+        <v>541115</v>
       </c>
       <c r="R29" t="n">
-        <v>7246534</v>
+        <v>7246606</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3987,10 +3987,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122118203</v>
+        <v>122118230</v>
       </c>
       <c r="B30" t="n">
-        <v>90819</v>
+        <v>78651</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4003,21 +4003,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541108</v>
+        <v>541091</v>
       </c>
       <c r="R30" t="n">
-        <v>7246632</v>
+        <v>7246477</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,6 +4065,11 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4086,12 +4091,12 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>granhögstubbe knäckt med fågelbo i toppen</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4112,7 +4117,7 @@
         <v>122118213</v>
       </c>
       <c r="B31" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4231,10 +4236,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122118229</v>
+        <v>122118172</v>
       </c>
       <c r="B32" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4247,34 +4252,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541121</v>
+        <v>541106</v>
       </c>
       <c r="R32" t="n">
-        <v>7246580</v>
+        <v>7246534</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4307,6 +4317,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4333,10 +4348,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122118171</v>
+        <v>122118229</v>
       </c>
       <c r="B33" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4349,39 +4364,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541115</v>
+        <v>541121</v>
       </c>
       <c r="R33" t="n">
-        <v>7246606</v>
+        <v>7246580</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4414,11 +4424,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack färska, lågt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4445,10 +4450,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122118230</v>
+        <v>122118203</v>
       </c>
       <c r="B34" t="n">
-        <v>78651</v>
+        <v>90826</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4461,21 +4466,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4485,10 +4490,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541091</v>
+        <v>541108</v>
       </c>
       <c r="R34" t="n">
-        <v>7246477</v>
+        <v>7246632</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4523,11 +4528,6 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4549,12 +4549,12 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>granhögstubbe knäckt med fågelbo i toppen</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -3875,7 +3875,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122118171</v>
+        <v>122118172</v>
       </c>
       <c r="B29" t="n">
         <v>57379</v>
@@ -3893,11 +3893,6 @@
       <c r="E29" t="n">
         <v>100109</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3920,10 +3915,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541115</v>
+        <v>541106</v>
       </c>
       <c r="R29" t="n">
-        <v>7246606</v>
+        <v>7246534</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3987,10 +3982,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122118230</v>
+        <v>122118229</v>
       </c>
       <c r="B30" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4005,11 +4000,6 @@
       <c r="E30" t="n">
         <v>6425</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4027,10 +4017,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541091</v>
+        <v>541121</v>
       </c>
       <c r="R30" t="n">
-        <v>7246477</v>
+        <v>7246580</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4065,11 +4055,6 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4078,26 +4063,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Död gran</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies # Död gran</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4114,10 +4079,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122118213</v>
+        <v>122118171</v>
       </c>
       <c r="B31" t="n">
-        <v>90826</v>
+        <v>57379</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4130,34 +4095,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541085</v>
+        <v>541115</v>
       </c>
       <c r="R31" t="n">
-        <v>7246493</v>
+        <v>7246606</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4192,6 +4157,11 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4200,26 +4170,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4236,10 +4186,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122118172</v>
+        <v>122118203</v>
       </c>
       <c r="B32" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4252,39 +4202,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541106</v>
+        <v>541108</v>
       </c>
       <c r="R32" t="n">
-        <v>7246534</v>
+        <v>7246632</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4319,11 +4259,6 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska, lågt</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4332,6 +4267,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>granhögstubbe knäckt med fågelbo i toppen</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4348,10 +4298,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122118229</v>
+        <v>122118230</v>
       </c>
       <c r="B33" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4366,11 +4316,6 @@
       <c r="E33" t="n">
         <v>6425</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4388,10 +4333,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541121</v>
+        <v>541091</v>
       </c>
       <c r="R33" t="n">
-        <v>7246580</v>
+        <v>7246477</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4426,6 +4371,11 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4434,6 +4384,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Död gran</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gran</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4450,10 +4415,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122118203</v>
+        <v>122118213</v>
       </c>
       <c r="B34" t="n">
-        <v>90826</v>
+        <v>90831</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4468,11 +4433,6 @@
       <c r="E34" t="n">
         <v>5432</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>Porodaedalea chrysoloma</t>
@@ -4490,10 +4450,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541108</v>
+        <v>541085</v>
       </c>
       <c r="R34" t="n">
-        <v>7246632</v>
+        <v>7246493</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4537,11 +4497,6 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK34" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -4549,12 +4504,12 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>granhögstubbe knäckt med fågelbo i toppen</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies # granhögstubbe knäckt med fågelbo i toppen</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -3982,10 +3982,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122118229</v>
+        <v>122118171</v>
       </c>
       <c r="B30" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3998,29 +3998,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541121</v>
+        <v>541115</v>
       </c>
       <c r="R30" t="n">
-        <v>7246580</v>
+        <v>7246606</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4053,6 +4058,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4079,10 +4089,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122118171</v>
+        <v>122118229</v>
       </c>
       <c r="B31" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4095,34 +4105,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541115</v>
+        <v>541121</v>
       </c>
       <c r="R31" t="n">
-        <v>7246606</v>
+        <v>7246580</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4155,11 +4160,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska, lågt</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -3982,10 +3982,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122118171</v>
+        <v>122118229</v>
       </c>
       <c r="B30" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3998,34 +3998,29 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541115</v>
+        <v>541121</v>
       </c>
       <c r="R30" t="n">
-        <v>7246606</v>
+        <v>7246580</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4058,11 +4053,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska, lågt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4089,10 +4079,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122118229</v>
+        <v>122118171</v>
       </c>
       <c r="B31" t="n">
-        <v>78652</v>
+        <v>57379</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4105,29 +4095,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541121</v>
+        <v>541115</v>
       </c>
       <c r="R31" t="n">
-        <v>7246580</v>
+        <v>7246606</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4160,6 +4155,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -3875,10 +3875,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122118172</v>
+        <v>122118171</v>
       </c>
       <c r="B29" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3893,6 +3893,11 @@
       <c r="E29" t="n">
         <v>100109</v>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3915,10 +3920,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541106</v>
+        <v>541115</v>
       </c>
       <c r="R29" t="n">
-        <v>7246534</v>
+        <v>7246606</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3985,7 +3990,7 @@
         <v>122118229</v>
       </c>
       <c r="B30" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3999,6 +4004,11 @@
       </c>
       <c r="E30" t="n">
         <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4079,10 +4089,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122118171</v>
+        <v>122118230</v>
       </c>
       <c r="B31" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4095,34 +4105,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541115</v>
+        <v>541091</v>
       </c>
       <c r="R31" t="n">
-        <v>7246606</v>
+        <v>7246477</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4159,7 +4169,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska, lågt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4170,6 +4180,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Död gran</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gran</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4189,7 +4219,7 @@
         <v>122118203</v>
       </c>
       <c r="B32" t="n">
-        <v>90831</v>
+        <v>90844</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4204,6 +4234,11 @@
       <c r="E32" t="n">
         <v>5432</v>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Porodaedalea chrysoloma</t>
@@ -4267,6 +4302,11 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
@@ -4298,10 +4338,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122118230</v>
+        <v>122118213</v>
       </c>
       <c r="B33" t="n">
-        <v>78652</v>
+        <v>90844</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4314,16 +4354,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4333,10 +4378,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541091</v>
+        <v>541085</v>
       </c>
       <c r="R33" t="n">
-        <v>7246477</v>
+        <v>7246493</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4371,11 +4416,6 @@
           <t>2025-01-04</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4385,6 +4425,11 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK33" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -4392,12 +4437,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4415,10 +4460,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122118213</v>
+        <v>122118172</v>
       </c>
       <c r="B34" t="n">
-        <v>90831</v>
+        <v>57383</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4431,29 +4476,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541085</v>
+        <v>541106</v>
       </c>
       <c r="R34" t="n">
-        <v>7246493</v>
+        <v>7246534</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4488,6 +4543,11 @@
           <t>2025-01-04</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska, lågt</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4496,21 +4556,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 6658-2021 artfynd.xlsx
+++ b/artfynd/A 6658-2021 artfynd.xlsx
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>
